--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:53:51+00:00</t>
+    <t>2026-07-23T14:32:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
+++ b/spec-tech/ig/CodeSystem-cs-xdm-association-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
